--- a/01_clientes/01_restaurante_teste_ativo/Planilha_Operacional_Restaurante_Teste.xlsx
+++ b/01_clientes/01_restaurante_teste_ativo/Planilha_Operacional_Restaurante_Teste.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="158">
   <si>
     <t>PASSO</t>
   </si>
@@ -1220,7 +1220,8 @@
   <dimension ref="A1:I411"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.44140625" customWidth="1"/>
     <col min="5" max="5" width="13.21875" bestFit="1" customWidth="1"/>
@@ -1505,7 +1506,9 @@
       <c r="C11" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>156</v>
+      </c>
       <c r="E11" s="7">
         <v>3</v>
       </c>
@@ -1555,7 +1558,9 @@
       <c r="C13" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D13" s="7"/>
+      <c r="D13" s="7" t="s">
+        <v>156</v>
+      </c>
       <c r="E13" s="7">
         <v>4</v>
       </c>
@@ -3559,8 +3564,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" customWidth="1"/>
+    <col min="3" max="3" width="27.88671875" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="12" customWidth="1"/>
   </cols>

--- a/01_clientes/01_restaurante_teste_ativo/Planilha_Operacional_Restaurante_Teste.xlsx
+++ b/01_clientes/01_restaurante_teste_ativo/Planilha_Operacional_Restaurante_Teste.xlsx
@@ -9,21 +9,22 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
     <sheet name="Produtos" sheetId="4" r:id="rId4"/>
-    <sheet name="GERENCIAL_PRIVADO" sheetId="5" r:id="rId5"/>
+    <sheet name="Impostos_monofasicos" sheetId="6" r:id="rId5"/>
+    <sheet name="GERENCIAL_PRIVADO" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="167">
   <si>
     <t>PASSO</t>
   </si>
@@ -497,6 +498,58 @@
   </si>
   <si>
     <t xml:space="preserve">SIM </t>
+  </si>
+  <si>
+    <t>item_produto</t>
+  </si>
+  <si>
+    <t>ncm</t>
+  </si>
+  <si>
+    <t>Cervejas de Malte</t>
+  </si>
+  <si>
+    <t>Refrigerantes</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>Águas Minerais / Gasosas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>Energéticos e Isotónicos</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Chá pronto para consumo </t>
+  </si>
+  <si>
+    <t>Café Espresso</t>
+  </si>
+  <si>
+    <t>Suco de Laranja Natural</t>
   </si>
 </sst>
 </file>
@@ -506,7 +559,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -541,8 +594,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -553,6 +624,12 @@
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
       </patternFill>
     </fill>
   </fills>
@@ -583,7 +660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -640,6 +717,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1257,7 +1343,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>46114</v>
       </c>
@@ -1284,7 +1370,7 @@
       </c>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>46115</v>
       </c>
@@ -1311,7 +1397,7 @@
       </c>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>46115</v>
       </c>
@@ -1338,7 +1424,7 @@
       </c>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="45" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>46116</v>
       </c>
@@ -1365,7 +1451,7 @@
       </c>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>46116</v>
       </c>
@@ -1392,7 +1478,7 @@
       </c>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="45" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>46117</v>
       </c>
@@ -1418,7 +1504,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>46117</v>
       </c>
@@ -1444,7 +1530,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>46118</v>
       </c>
@@ -1470,7 +1556,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>46118</v>
       </c>
@@ -1496,7 +1582,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="45" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>46119</v>
       </c>
@@ -1522,7 +1608,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>46119</v>
       </c>
@@ -1548,7 +1634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>46120</v>
       </c>
@@ -1574,7 +1660,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>46120</v>
       </c>
@@ -1600,7 +1686,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>46121</v>
       </c>
@@ -1626,7 +1712,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>46121</v>
       </c>
@@ -1652,7 +1738,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>46122</v>
       </c>
@@ -1678,7 +1764,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>46122</v>
       </c>
@@ -3717,7 +3803,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>63</v>
       </c>
@@ -3811,6 +3897,84 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="22">
+        <v>22030000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="22">
+        <v>22021000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="22">
+        <v>22011000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="22">
+        <v>22029900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="22">
+        <v>22021000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="24">
+        <v>9012100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="24">
+        <v>20091900</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
